--- a/Result/profitability/8249.xlsx
+++ b/Result/profitability/8249.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.04</v>
       </c>
       <c r="M2" t="n">
-        <v>0.87</v>
+        <v>0.6475000000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>18.6075</v>
+        <v>17.9025</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.24</v>
       </c>
       <c r="M3" t="n">
-        <v>0.5887500000000001</v>
+        <v>0.5475000000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>16.685</v>
+        <v>15.97875</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.3</v>
       </c>
       <c r="M4" t="n">
-        <v>0.55625</v>
+        <v>0.4550000000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>15.25875</v>
+        <v>14.405</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.05</v>
       </c>
       <c r="M5" t="n">
-        <v>0.4325000000000001</v>
+        <v>0.33125</v>
       </c>
       <c r="N5" t="n">
-        <v>13.07</v>
+        <v>12.35625</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.25</v>
       </c>
       <c r="M6" t="n">
-        <v>0.27125</v>
+        <v>0.08375000000000005</v>
       </c>
       <c r="N6" t="n">
-        <v>10.075</v>
+        <v>9.547499999999999</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.46</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1125000000000001</v>
+        <v>0.1100000000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>8.5375</v>
+        <v>8.0425</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.59</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1550000000000001</v>
+        <v>0.1375000000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>7.5675</v>
+        <v>7.382499999999999</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>8249</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>996</v>
+      </c>
+      <c r="D75" t="n">
+        <v>844</v>
+      </c>
+      <c r="E75" t="n">
+        <v>152</v>
+      </c>
+      <c r="F75" t="n">
+        <v>15.27</v>
+      </c>
+      <c r="G75" t="n">
+        <v>58</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>5.84%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-26</v>
+      </c>
+      <c r="J75" t="n">
+        <v>32</v>
+      </c>
+      <c r="K75" t="n">
+        <v>25</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.9037500000000001</v>
+      </c>
+      <c r="N75" t="n">
+        <v>19.45625</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.3783783783783784</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-1.48</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.08835820895522395</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.8100000000000001</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.7788461538461539</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-5.710000000000001</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.2721639656816015</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
